--- a/artfynd/A 27574-2025 artfynd.xlsx
+++ b/artfynd/A 27574-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>7001851</v>
       </c>
       <c r="B2" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411505.8891984265</v>
+        <v>411506</v>
       </c>
       <c r="R2" t="n">
-        <v>6963380.517232755</v>
+        <v>6963381</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2013-10-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7001850</v>
+        <v>7001849</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411414.8097459204</v>
+        <v>411415</v>
       </c>
       <c r="R3" t="n">
-        <v>6963301.473262857</v>
+        <v>6963301</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2013-10-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7001849</v>
+        <v>7001930</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411414.8097459204</v>
+        <v>411307</v>
       </c>
       <c r="R4" t="n">
-        <v>6963301.473262857</v>
+        <v>6963439</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2013-10-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95113780</v>
+        <v>127743723</v>
       </c>
       <c r="B5" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220686</v>
+        <v>5454</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,27 +1011,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnhåberget, Berg, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411743.2644444637</v>
+        <v>411872</v>
       </c>
       <c r="R5" t="n">
-        <v>6963512.399678896</v>
+        <v>6963734</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,22 +1047,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,15 +1077,562 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>88694194</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sölvbacka strömmar, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>411746</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6963102</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-07-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-07-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127743725</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>411979</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6963786</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7001850</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björnhåberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>411415</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6963301</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2013-10-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2013-10-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127743720</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>411710</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6963703</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>95113780</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnhåberget, Berg, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>411743</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6963513</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-07-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-07-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Håkan Sundin</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Håkan Sundin, Eva Sundin</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
